--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.93751942190308</v>
+        <v>7.62734690605925</v>
       </c>
       <c r="D2" t="n">
-        <v>52.38813195700015</v>
+        <v>8.513071443012524</v>
       </c>
       <c r="E2" t="n">
-        <v>11.88031555157018</v>
+        <v>1.930551277130155</v>
       </c>
       <c r="F2" t="n">
-        <v>11.89560462341977</v>
+        <v>1.933035751305714</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.68970899296238</v>
+        <v>3.037077711356386</v>
       </c>
       <c r="D3" t="n">
-        <v>28.02508890213173</v>
+        <v>4.554076946596407</v>
       </c>
       <c r="E3" t="n">
-        <v>11.88031555157018</v>
+        <v>1.930551277130155</v>
       </c>
       <c r="F3" t="n">
-        <v>11.89560462341977</v>
+        <v>1.933035751305714</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.35434585311004</v>
+        <v>6.720081201130382</v>
       </c>
       <c r="D4" t="n">
-        <v>42.9418045431973</v>
+        <v>6.978043238269562</v>
       </c>
       <c r="E4" t="n">
-        <v>11.88031555157018</v>
+        <v>1.930551277130155</v>
       </c>
       <c r="F4" t="n">
-        <v>11.89560462341977</v>
+        <v>1.933035751305714</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.86819758003454</v>
+        <v>5.178582106755612</v>
       </c>
       <c r="D5" t="n">
-        <v>32.25351133046873</v>
+        <v>5.241195591201169</v>
       </c>
       <c r="E5" t="n">
-        <v>11.88031555157018</v>
+        <v>1.930551277130155</v>
       </c>
       <c r="F5" t="n">
-        <v>11.89560462341977</v>
+        <v>1.933035751305714</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.62999860760283</v>
+        <v>3.51487477373546</v>
       </c>
       <c r="D6" t="n">
-        <v>20.21674879575812</v>
+        <v>3.285221679310694</v>
       </c>
       <c r="E6" t="n">
-        <v>11.88031555157018</v>
+        <v>1.930551277130155</v>
       </c>
       <c r="F6" t="n">
-        <v>11.89560462341977</v>
+        <v>1.933035751305714</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8.496147892507599</v>
+        <v>1.380624032532485</v>
       </c>
       <c r="D7" t="n">
-        <v>44.60108707096866</v>
+        <v>7.247676649032408</v>
       </c>
       <c r="E7" t="n">
-        <v>11.88031555157018</v>
+        <v>1.930551277130155</v>
       </c>
       <c r="F7" t="n">
-        <v>11.89560462341977</v>
+        <v>1.933035751305714</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.71321103577289</v>
+        <v>3.690896793313094</v>
       </c>
       <c r="D8" t="n">
-        <v>44.32522506550946</v>
+        <v>7.202849073145289</v>
       </c>
       <c r="E8" t="n">
-        <v>11.88031555157018</v>
+        <v>1.930551277130155</v>
       </c>
       <c r="F8" t="n">
-        <v>11.89560462341977</v>
+        <v>1.933035751305714</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.81015698049727</v>
+        <v>5.494150509330806</v>
       </c>
       <c r="D9" t="n">
-        <v>34.00458899330395</v>
+        <v>5.525745711411892</v>
       </c>
       <c r="E9" t="n">
-        <v>11.88031555157018</v>
+        <v>1.930551277130155</v>
       </c>
       <c r="F9" t="n">
-        <v>11.89560462341977</v>
+        <v>1.933035751305714</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>15.22910499220108</v>
+        <v>2.474729561232675</v>
       </c>
       <c r="D10" t="n">
-        <v>13.69311025077803</v>
+        <v>2.225130415751429</v>
       </c>
       <c r="E10" t="n">
-        <v>11.88031555157018</v>
+        <v>1.930551277130155</v>
       </c>
       <c r="F10" t="n">
-        <v>11.89560462341977</v>
+        <v>1.933035751305714</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
